--- a/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E7" s="2">
         <v>44954</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44590</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44226</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43498</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43134</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42763</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42399</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>19968700</v>
+      </c>
+      <c r="E8" s="3">
         <v>19315200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16667300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15430000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13190700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13007300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12754600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12350500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12467600</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16326100</v>
+      </c>
+      <c r="E9" s="3">
         <v>15883700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13588600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12451100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10763900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10646500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10513500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10223000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10476500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3642600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3431500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3078700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2979000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2426800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2360900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2241100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2127500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1991000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,27 +961,30 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E14" s="3">
         <v>15600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,30 +1000,33 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>11000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11900</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1042,8 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19170100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18580400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16050600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14791700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12842300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12703900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12534300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12134500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12280800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>798600</v>
+      </c>
+      <c r="E18" s="3">
         <v>734700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>616700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>638300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>348400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>303500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>220300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>216000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>186800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,26 +1179,27 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1176,8 +1209,8 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1188,36 +1221,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1026600</v>
+      </c>
+      <c r="E21" s="3">
         <v>934800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>789700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>797000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>503000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>465700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>384300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>394300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,39 +1266,42 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E22" s="3">
         <v>43300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>51300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>71500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>102000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>164500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>196700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>143400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>150100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>735900</v>
+      </c>
+      <c r="E23" s="3">
         <v>690500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>557900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>558000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>244000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>138900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>72700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>212200</v>
+      </c>
+      <c r="E24" s="3">
         <v>176300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>131100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>136800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E26" s="3">
         <v>514300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>426800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>421200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>187800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>124700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>44700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E27" s="3">
         <v>514300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>426800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>421200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>187800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>124700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>44700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,39 +1581,42 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>2600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>30400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-600</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,27 +1716,30 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1680,8 +1749,8 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E33" s="3">
         <v>513200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>426700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>421000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>187200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>127300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>44200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E35" s="3">
         <v>513200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>426700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>421000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>187200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>127300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>44200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E38" s="2">
         <v>44954</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44590</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44226</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43498</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43134</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42763</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42399</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1987,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E41" s="3">
         <v>33900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,9 +2029,12 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,36 +2074,39 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>234800</v>
+      </c>
+      <c r="E43" s="3">
         <v>239700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>174000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>172700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>206400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>194300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>190800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>166200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,36 +2119,39 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1454800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1378600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1242900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1205700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1081500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1052300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1019100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1031800</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2069,36 +2164,39 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E45" s="3">
         <v>51000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>54700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>91800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2209,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1794000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1703200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1517100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1470600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1360000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1337200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1336600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1264400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,9 +2254,12 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2195,36 +2299,39 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3719300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3480000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3074300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2856600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2820300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>748800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>758800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>763600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,36 +2344,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1116400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1124300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1048800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1059300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1071100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1125000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1149000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1177300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,36 +2479,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E52" s="3">
         <v>42400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2569,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6677600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6350000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5668900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5411500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5269800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3239300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3273900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3232200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2655,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1183300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1195700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1112800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>988100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>786400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>816900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>751900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>720600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,36 +2697,39 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>326000</v>
+      </c>
+      <c r="E58" s="3">
         <v>406600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>260000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>343400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>254400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>219800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,36 +2742,39 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>958700</v>
+      </c>
+      <c r="E59" s="3">
         <v>943000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>888400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>783100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>671600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>506400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>497900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>459700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2787,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2468000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2545300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2002500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2031200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1801400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1577700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1469600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1200300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,36 +2832,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>460900</v>
+      </c>
+      <c r="E61" s="3">
         <v>475300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>763400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>860300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1352500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1575300</v>
       </c>
-      <c r="I61" s="3">
-        <v>2499200</v>
-      </c>
       <c r="J61" s="3">
+        <v>2492700</v>
+      </c>
+      <c r="K61" s="3">
         <v>2000100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,36 +2877,39 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2289800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2282500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2254900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2170200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>285900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>324500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>364600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3057,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5218800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5303100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5020800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5092200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5324100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3441400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4293300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3571300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,36 +3301,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1168200</v>
+      </c>
+      <c r="E72" s="3">
         <v>644500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>131300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-295300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-716400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-915100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1036000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-356800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3481,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1458900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1046800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>648100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>319300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-54300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-202100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1019400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-339100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E80" s="2">
         <v>44954</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44590</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44226</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43498</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43134</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42763</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42399</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>523700</v>
+      </c>
+      <c r="E81" s="3">
         <v>513200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>426700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>421000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>187200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>127300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>44200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>227700</v>
+      </c>
+      <c r="E83" s="3">
         <v>200900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>180500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>167500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>157000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>162200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>164100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>178300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3955,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>718900</v>
+      </c>
+      <c r="E89" s="3">
         <v>788200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>831700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>868500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>355100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>427100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>210100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>297400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-467100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-397800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-323600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-218300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-196900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-145900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-137500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-114800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-454800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-747100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-304500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-192400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-175300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-145900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-137500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-262000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-52600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-525200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-662800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-176800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-289000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-69600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-188100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,9 +4443,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,14 +4473,14 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4240,36 +4488,39 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -977,19 +977,19 @@
         <v>15600</v>
       </c>
       <c r="F14" s="3">
-        <v>700</v>
+        <v>18200</v>
       </c>
       <c r="G14" s="3">
         <v>4100</v>
       </c>
       <c r="H14" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>3800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>29400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>30100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12300</v>
+        <v>227700</v>
       </c>
       <c r="E15" s="3">
-        <v>11000</v>
+        <v>200900</v>
       </c>
       <c r="F15" s="3">
-        <v>10500</v>
+        <v>180500</v>
       </c>
       <c r="G15" s="3">
-        <v>11900</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>167500</v>
+      </c>
+      <c r="H15" s="3">
+        <v>157000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>162200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>164100</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19170100</v>
+        <v>19154300</v>
       </c>
       <c r="E17" s="3">
-        <v>18580400</v>
+        <v>18564900</v>
       </c>
       <c r="F17" s="3">
-        <v>16050600</v>
+        <v>16032500</v>
       </c>
       <c r="G17" s="3">
-        <v>14791700</v>
+        <v>14787600</v>
       </c>
       <c r="H17" s="3">
-        <v>12842300</v>
+        <v>12838500</v>
       </c>
       <c r="I17" s="3">
-        <v>12703900</v>
+        <v>12699900</v>
       </c>
       <c r="J17" s="3">
-        <v>12534300</v>
+        <v>12525300</v>
       </c>
       <c r="K17" s="3">
         <v>12134500</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>798600</v>
+        <v>814400</v>
       </c>
       <c r="E18" s="3">
-        <v>734700</v>
+        <v>750300</v>
       </c>
       <c r="F18" s="3">
-        <v>616700</v>
+        <v>634800</v>
       </c>
       <c r="G18" s="3">
-        <v>638300</v>
+        <v>642400</v>
       </c>
       <c r="H18" s="3">
-        <v>348400</v>
+        <v>352200</v>
       </c>
       <c r="I18" s="3">
-        <v>303500</v>
+        <v>307400</v>
       </c>
       <c r="J18" s="3">
-        <v>220300</v>
+        <v>229300</v>
       </c>
       <c r="K18" s="3">
         <v>216000</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
-        <v>-900</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>6300</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1026600</v>
+        <v>1042700</v>
       </c>
       <c r="E21" s="3">
-        <v>934800</v>
+        <v>951400</v>
       </c>
       <c r="F21" s="3">
-        <v>789700</v>
+        <v>809000</v>
       </c>
       <c r="G21" s="3">
-        <v>797000</v>
+        <v>809800</v>
       </c>
       <c r="H21" s="3">
-        <v>503000</v>
+        <v>509200</v>
       </c>
       <c r="I21" s="3">
-        <v>465700</v>
+        <v>469600</v>
       </c>
       <c r="J21" s="3">
-        <v>384300</v>
+        <v>393400</v>
       </c>
       <c r="K21" s="3">
         <v>394300</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>63000</v>
+        <v>62100</v>
       </c>
       <c r="E22" s="3">
-        <v>43300</v>
+        <v>41600</v>
       </c>
       <c r="F22" s="3">
-        <v>51300</v>
+        <v>49100</v>
       </c>
       <c r="G22" s="3">
-        <v>71500</v>
+        <v>75900</v>
       </c>
       <c r="H22" s="3">
-        <v>102000</v>
+        <v>99200</v>
       </c>
       <c r="I22" s="3">
-        <v>164500</v>
+        <v>132600</v>
       </c>
       <c r="J22" s="3">
-        <v>196700</v>
+        <v>167200</v>
       </c>
       <c r="K22" s="3">
         <v>143400</v>
@@ -1381,10 +1381,10 @@
         <v>56200</v>
       </c>
       <c r="I24" s="3">
-        <v>14200</v>
+        <v>11800</v>
       </c>
       <c r="J24" s="3">
-        <v>3700</v>
+        <v>-28400</v>
       </c>
       <c r="K24" s="3">
         <v>28000</v>
@@ -1471,10 +1471,10 @@
         <v>187800</v>
       </c>
       <c r="I26" s="3">
-        <v>124700</v>
+        <v>127100</v>
       </c>
       <c r="J26" s="3">
-        <v>19900</v>
+        <v>52000</v>
       </c>
       <c r="K26" s="3">
         <v>44700</v>
@@ -1504,22 +1504,22 @@
         <v>523700</v>
       </c>
       <c r="E27" s="3">
-        <v>514300</v>
+        <v>513200</v>
       </c>
       <c r="F27" s="3">
-        <v>426800</v>
+        <v>426600</v>
       </c>
       <c r="G27" s="3">
-        <v>421200</v>
+        <v>421000</v>
       </c>
       <c r="H27" s="3">
-        <v>187800</v>
+        <v>187200</v>
       </c>
       <c r="I27" s="3">
-        <v>124700</v>
+        <v>127300</v>
       </c>
       <c r="J27" s="3">
-        <v>19900</v>
+        <v>50300</v>
       </c>
       <c r="K27" s="3">
         <v>44700</v>
@@ -1606,10 +1606,10 @@
         <v>-600</v>
       </c>
       <c r="I29" s="3">
-        <v>2600</v>
+        <v>200</v>
       </c>
       <c r="J29" s="3">
-        <v>30400</v>
+        <v>-1700</v>
       </c>
       <c r="K29" s="3">
         <v>-500</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>-6300</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2173,26 +2173,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>68400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>51000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>54700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>48600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>42000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>63500</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
-        <v>91800</v>
+        <v>9800</v>
       </c>
       <c r="K45" s="3">
         <v>34300</v>
@@ -2263,26 +2263,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47900</v>
+        <v>43800</v>
       </c>
       <c r="E52" s="3">
-        <v>42400</v>
+        <v>30900</v>
       </c>
       <c r="F52" s="3">
-        <v>28700</v>
+        <v>23200</v>
       </c>
       <c r="G52" s="3">
-        <v>25100</v>
+        <v>19400</v>
       </c>
       <c r="H52" s="3">
         <v>18400</v>
@@ -2707,22 +2707,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>326000</v>
+        <v>479700</v>
       </c>
       <c r="E58" s="3">
-        <v>406600</v>
+        <v>583900</v>
       </c>
       <c r="F58" s="3">
-        <v>1300</v>
+        <v>144900</v>
       </c>
       <c r="G58" s="3">
-        <v>260000</v>
+        <v>391500</v>
       </c>
       <c r="H58" s="3">
-        <v>343400</v>
+        <v>467100</v>
       </c>
       <c r="I58" s="3">
-        <v>254400</v>
+        <v>258900</v>
       </c>
       <c r="J58" s="3">
         <v>219800</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>958700</v>
+        <v>572200</v>
       </c>
       <c r="E59" s="3">
-        <v>943000</v>
+        <v>504300</v>
       </c>
       <c r="F59" s="3">
-        <v>888400</v>
+        <v>426500</v>
       </c>
       <c r="G59" s="3">
-        <v>783100</v>
+        <v>353500</v>
       </c>
       <c r="H59" s="3">
-        <v>671600</v>
+        <v>328900</v>
       </c>
       <c r="I59" s="3">
-        <v>506400</v>
+        <v>265100</v>
       </c>
       <c r="J59" s="3">
-        <v>497900</v>
+        <v>250100</v>
       </c>
       <c r="K59" s="3">
         <v>459700</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>460900</v>
+        <v>2511800</v>
       </c>
       <c r="E61" s="3">
-        <v>475300</v>
+        <v>2534100</v>
       </c>
       <c r="F61" s="3">
-        <v>763400</v>
+        <v>2823100</v>
       </c>
       <c r="G61" s="3">
-        <v>860300</v>
+        <v>2874400</v>
       </c>
       <c r="H61" s="3">
-        <v>1352500</v>
+        <v>3378600</v>
       </c>
       <c r="I61" s="3">
-        <v>1575300</v>
+        <v>1619700</v>
       </c>
       <c r="J61" s="3">
-        <v>2492700</v>
+        <v>2527800</v>
       </c>
       <c r="K61" s="3">
         <v>2000100</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2289800</v>
+        <v>143500</v>
       </c>
       <c r="E62" s="3">
-        <v>2282500</v>
+        <v>142000</v>
       </c>
       <c r="F62" s="3">
-        <v>2254900</v>
+        <v>120200</v>
       </c>
       <c r="G62" s="3">
-        <v>2200700</v>
+        <v>128900</v>
       </c>
       <c r="H62" s="3">
-        <v>2170200</v>
+        <v>82000</v>
       </c>
       <c r="I62" s="3">
-        <v>285900</v>
+        <v>171300</v>
       </c>
       <c r="J62" s="3">
-        <v>324500</v>
+        <v>210000</v>
       </c>
       <c r="K62" s="3">
         <v>364600</v>
@@ -3085,7 +3085,7 @@
         <v>3441400</v>
       </c>
       <c r="J66" s="3">
-        <v>4293300</v>
+        <v>4303700</v>
       </c>
       <c r="K66" s="3">
         <v>3571300</v>
@@ -3509,7 +3509,7 @@
         <v>-202100</v>
       </c>
       <c r="J76" s="3">
-        <v>-1019400</v>
+        <v>-1029900</v>
       </c>
       <c r="K76" s="3">
         <v>-339100</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>227700</v>
+        <v>219800</v>
       </c>
       <c r="E83" s="3">
-        <v>200900</v>
+        <v>191700</v>
       </c>
       <c r="F83" s="3">
-        <v>180500</v>
+        <v>170000</v>
       </c>
       <c r="G83" s="3">
-        <v>167500</v>
+        <v>155600</v>
       </c>
       <c r="H83" s="3">
-        <v>157000</v>
+        <v>143500</v>
       </c>
       <c r="I83" s="3">
-        <v>162200</v>
+        <v>140400</v>
       </c>
       <c r="J83" s="3">
-        <v>164100</v>
+        <v>138100</v>
       </c>
       <c r="K83" s="3">
         <v>178300</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45325</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44954</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44590</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44226</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43498</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43134</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42763</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42399</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20501800</v>
+      </c>
+      <c r="E8" s="3">
         <v>19968700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19315200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16667300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15430000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13190700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13007300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12754600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12350500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12467600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16737400</v>
+      </c>
+      <c r="E9" s="3">
         <v>16326100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15883700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13588600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12451100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10763900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10646500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10513500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10223000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10476500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3764400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3642600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3431500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3078700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2979000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2426800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2360900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2241100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2127500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1991000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,36 +980,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E14" s="3">
         <v>15800</v>
       </c>
-      <c r="E14" s="3">
-        <v>15600</v>
-      </c>
       <c r="F14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G14" s="3">
         <v>18200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,50 +1022,53 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E15" s="3">
         <v>227700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>200900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>180500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>167500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>157000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>162200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>164100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19721200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19154300</v>
       </c>
-      <c r="E17" s="3">
-        <v>18564900</v>
-      </c>
       <c r="F17" s="3">
+        <v>18577200</v>
+      </c>
+      <c r="G17" s="3">
         <v>16032500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14787600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12838500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12699900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12525300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12134500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12280800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>780600</v>
+      </c>
+      <c r="E18" s="3">
         <v>814400</v>
       </c>
-      <c r="E18" s="3">
-        <v>750300</v>
-      </c>
       <c r="F18" s="3">
+        <v>738000</v>
+      </c>
+      <c r="G18" s="3">
         <v>634800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>642400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>352200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>307400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>229300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>216000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>186800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,23 +1212,24 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>6300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1206,14 +1239,14 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1224,9 +1257,12 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1234,29 +1270,29 @@
         <v>1042700</v>
       </c>
       <c r="E21" s="3">
-        <v>951400</v>
+        <v>1042100</v>
       </c>
       <c r="F21" s="3">
+        <v>938900</v>
+      </c>
+      <c r="G21" s="3">
         <v>809000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>809800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>509200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>469600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>393400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>394300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,42 +1305,45 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>62100</v>
+        <v>49500</v>
       </c>
       <c r="E22" s="3">
-        <v>41600</v>
+        <v>62300</v>
       </c>
       <c r="F22" s="3">
+        <v>41800</v>
+      </c>
+      <c r="G22" s="3">
         <v>49100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>75900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>99200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>132600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>167200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>143400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>150100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>720800</v>
+      </c>
+      <c r="E23" s="3">
         <v>735900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>690500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>557900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>558000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>244000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>138900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>72700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36700</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>186400</v>
+      </c>
+      <c r="E24" s="3">
         <v>212200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>176300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>131100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>136800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-28400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E26" s="3">
         <v>523700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>514300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>426800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>421200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>187800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>127100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>52000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E27" s="3">
         <v>523700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>513200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>426600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>421000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>187200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>127300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,42 +1641,45 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-1700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-600</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,24 +1785,27 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>200</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1746,14 +1815,14 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E33" s="3">
         <v>523700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>513200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>426700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>421000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>187200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>127300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>44200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E35" s="3">
         <v>523700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>513200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>426700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>421000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>187200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>127300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>44200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45325</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44954</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44590</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44226</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43498</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43134</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42763</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42399</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,38 +2073,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E41" s="3">
         <v>36000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,9 +2118,12 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2077,39 +2166,42 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E43" s="3">
         <v>234800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>239700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>174000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>172700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>206400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>194300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>190800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>166200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,39 +2214,42 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1509000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1454800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1378600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1242900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1205700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1081500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1052300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1019100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1031800</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,9 +2262,12 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2191,15 +2289,15 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>9800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,39 +2310,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1879000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1794000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1703200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1517100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1470600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1360000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1337200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1336600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1264400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,9 +2358,12 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2284,8 +2388,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2302,39 +2406,42 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3997900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3719300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3480000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3074300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2856600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2820300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>748800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>758800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>763600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,39 +2454,42 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1109900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1116400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1124300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1048800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1059300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1071100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1125000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1149000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1177300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,39 +2598,42 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E52" s="3">
         <v>43800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,39 +2694,42 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7065300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6677600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6350000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5668900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5411500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5269800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3239300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3273900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3232200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,38 +2785,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1253500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1183300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1195700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1112800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>988100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>786400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>816900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>751900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>720600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,39 +2830,42 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>375800</v>
+      </c>
+      <c r="E58" s="3">
         <v>479700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>583900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>144900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>391500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>467100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>258900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>219800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,39 +2878,42 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E59" s="3">
         <v>572200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>504300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>426500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>353500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>328900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>265100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>250100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>459700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,39 +2926,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2534100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2468000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2545300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2002500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2031200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1801400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1577700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1469600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,39 +2974,42 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2476400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2511800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2534100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2823100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2874400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3378600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1619700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2527800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2000100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,39 +3022,42 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E62" s="3">
         <v>143500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>142000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>120200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>128900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>82000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>171300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>210000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>364600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,39 +3214,42 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5217900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5218800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5303100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5020800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5092200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5324100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3441400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4303700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3571300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,39 +3474,42 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1702600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1168200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>644500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>131300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-295300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-716400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-915100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1036000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-356800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,39 +3666,42 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1847500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1458900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1046800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>648100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>319300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-54300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-202100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1029900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-339100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45325</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44954</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44590</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44226</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43498</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43134</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42763</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42399</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E81" s="3">
         <v>523700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>513200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>426700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>421000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>187200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>127300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>44200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,38 +3886,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>255600</v>
+      </c>
+      <c r="E83" s="3">
         <v>219800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>191700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>170000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>155600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>143500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>140400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>138100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>178300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,39 +4171,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>900900</v>
+      </c>
+      <c r="E89" s="3">
         <v>718900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>788200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>831700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>868500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>355100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>427100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>210100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>297400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,38 +4242,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-588000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-467100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-397800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-323600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-218300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-196900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-145900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-137500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-114800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,39 +4383,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-589600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-454800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-747100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-304500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-192400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-175300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-145900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-137500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-114800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,39 +4643,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-319100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-262000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-52600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-525200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-662800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-176800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-289000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-69600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-188100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,9 +4691,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,17 +4721,17 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4491,39 +4739,42 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BJ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44590</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44226</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43862</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43498</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43134</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42763</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42399</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,45 +723,48 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21457300</v>
+      </c>
+      <c r="E8" s="3">
         <v>20501800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19968700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19315200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16667300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15430000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13190700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13007300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12754600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12350500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12467600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -771,45 +774,48 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17457700</v>
+      </c>
+      <c r="E9" s="3">
         <v>16737400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16326100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15883700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13588600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12451100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10763900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10646500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10513500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10223000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10476500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,45 +825,48 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3999600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3764400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3642600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3431500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3078700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2979000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2426800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2360900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2241100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2127500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1991000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,39 +999,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>9300</v>
       </c>
-      <c r="E14" s="3">
-        <v>15800</v>
-      </c>
       <c r="F14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1025,53 +1044,56 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>288600</v>
+      </c>
+      <c r="E15" s="3">
         <v>262100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>227700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>200900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>180500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>167500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>157000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>162200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>164100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,44 +1122,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20636600</v>
+      </c>
+      <c r="E17" s="3">
         <v>19721200</v>
       </c>
-      <c r="E17" s="3">
-        <v>19154300</v>
-      </c>
       <c r="F17" s="3">
+        <v>19168300</v>
+      </c>
+      <c r="G17" s="3">
         <v>18577200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16032500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14787600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12838500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12699900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12525300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12134500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12280800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,45 +1170,48 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>820700</v>
+      </c>
+      <c r="E18" s="3">
         <v>780600</v>
       </c>
-      <c r="E18" s="3">
-        <v>814400</v>
-      </c>
       <c r="F18" s="3">
+        <v>800400</v>
+      </c>
+      <c r="G18" s="3">
         <v>738000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>634800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>642400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>352200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>307400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>229300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>216000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>186800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,9 +1221,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,8 +1245,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1227,12 +1260,12 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>6300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1242,14 +1275,14 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1260,42 +1293,45 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1109300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1042700</v>
       </c>
-      <c r="E21" s="3">
-        <v>1042100</v>
-      </c>
       <c r="F21" s="3">
+        <v>1028100</v>
+      </c>
+      <c r="G21" s="3">
         <v>938900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>809000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>809800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>509200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>469600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>393400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>394300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,45 +1344,48 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E22" s="3">
         <v>49500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>62300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>41800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>75900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>99200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>167200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>143400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>150100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,45 +1395,48 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>774200</v>
+      </c>
+      <c r="E23" s="3">
         <v>720800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>735900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>690500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>557900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>558000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>244000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>138900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>72700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>36700</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,45 +1446,48 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E24" s="3">
         <v>186400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>212200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>176300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>131100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>136800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-28400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1452,9 +1497,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,45 +1548,48 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E26" s="3">
         <v>534400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>523700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>514300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>426800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>421200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>187800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>127100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>52000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24700</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,45 +1599,48 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E27" s="3">
         <v>534400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>523700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>513200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>426600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>421000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>187200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>127300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>44700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24700</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1596,9 +1650,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1654,35 +1714,35 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-600</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,9 +1854,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1803,12 +1872,12 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,14 +1887,14 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1836,45 +1905,48 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E33" s="3">
         <v>534400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>523700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>513200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>426700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>421000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>187200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>127300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>44200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1884,9 +1956,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,45 +2007,48 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E35" s="3">
         <v>534400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>523700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>513200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>426700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>421000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>187200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>127300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>44200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,50 +2058,53 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44590</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44226</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43862</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43498</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43134</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42763</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42399</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2033,9 +2114,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,41 +2159,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E41" s="3">
         <v>28300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,9 +2207,12 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2169,42 +2258,45 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E43" s="3">
         <v>277300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>234800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>239700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>174000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>172700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>206400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>194300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>190800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>166200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,42 +2309,45 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1555500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1509000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1454800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1378600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1242900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1205700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1081500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1052300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1019100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1031800</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2265,9 +2360,12 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2292,15 +2390,15 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>9800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,42 +2411,45 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1990100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1879000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1794000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1703200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1517100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1470600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1360000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1337200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1336600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1264400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2462,12 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2391,8 +2495,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2409,42 +2513,45 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4340600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3997900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3719300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3480000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3074300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2856600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2820300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>748800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>758800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>763600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,42 +2564,45 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1104300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1109900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1116400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1124300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1048800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1059300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1071100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1125000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1149000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1177300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,42 +2717,45 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E52" s="3">
         <v>71600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,42 +2819,45 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7510500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7065300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6677600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6350000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5668900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5411500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5269800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3239300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3273900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3232200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,9 +2870,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,41 +2915,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1307400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1253500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1183300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1195700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1112800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>988100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>786400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>816900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>751900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>720600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,42 +2963,45 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>341500</v>
+      </c>
+      <c r="E58" s="3">
         <v>375800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>479700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>583900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>144900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>391500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>467100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>258900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>219800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,42 +3014,45 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>634500</v>
+      </c>
+      <c r="E59" s="3">
         <v>616300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>572200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>504300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>426500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>353500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>328900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>265100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>250100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>459700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,42 +3065,45 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2670200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2534100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2468000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2545300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2002500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2031200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1801400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1577700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1469600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,42 +3116,45 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2396800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2476400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2511800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2534100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2823100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2874400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3378600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1619700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2527800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2000100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3025,42 +3167,45 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E62" s="3">
         <v>132200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>143500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>142000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>120200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>128900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>82000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>171300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>210000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>364600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,42 +3371,45 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5312800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5217900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5218800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5303100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5020800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5092200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5324100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3441400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4303700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3571300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,9 +3422,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,42 +3647,45 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1201200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1702600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1168200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>644500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>131300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-295300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-716400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-915100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1036000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-356800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,9 +3698,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,42 +3851,45 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2197700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1847500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1458900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1046800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>648100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>319300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-54300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-202100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1029900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-339100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,9 +3902,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,50 +3953,53 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44590</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44226</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43862</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43498</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43134</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42763</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42399</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3818,45 +4009,48 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E81" s="3">
         <v>534400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>523700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>513200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>426700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>421000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>187200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>127300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>44200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,9 +4060,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,41 +4084,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E83" s="3">
         <v>255600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>219800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>191700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>170000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>155600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>143500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>140400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>138100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>178300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,9 +4132,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,42 +4387,45 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1030100</v>
+      </c>
+      <c r="E89" s="3">
         <v>900900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>718900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>788200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>831700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>868500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>355100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>427100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>210100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>297400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,9 +4438,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,41 +4462,42 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-702000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-588000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-467100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-397800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-323600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-218300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-196900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-145900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-137500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-114800</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4290,9 +4510,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,42 +4612,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-702300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-589600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-454800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-747100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-304500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-192400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-175300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-145900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-137500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-114800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4434,9 +4663,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,42 +4888,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-309700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-319100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-262000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-52600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-525200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-662800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-176800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-289000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-69600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-188100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,9 +4939,12 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,17 +4972,17 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4742,42 +4990,45 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,7 +5041,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
